--- a/power_output.xlsx
+++ b/power_output.xlsx
@@ -413,242 +413,677 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Sih1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Sih2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Pih1</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Pih2</t>
+          <t>Sub:1:Ln:1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2500.000000000006</v>
-      </c>
-      <c r="B2" t="n">
-        <v>249.9999999999969</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.00000000000044</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2499.895609982507</v>
-      </c>
-      <c r="E2" t="n">
-        <v>249.989560998247</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.99973902359451</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2500.000000000006</v>
-      </c>
-      <c r="B3" t="n">
-        <v>249.9999999999965</v>
-      </c>
-      <c r="C3" t="n">
-        <v>25.00000000000109</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2499.895609982507</v>
-      </c>
-      <c r="E3" t="n">
-        <v>249.9895609982466</v>
-      </c>
-      <c r="F3" t="n">
-        <v>24.99973902359516</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IH1S</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IH2S</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>IH1P</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IH2P</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FQ</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>IH1Q</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IH2Q</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2500.000000000003</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>250.0000000000022</v>
+        <v>0.008264487419915201</v>
       </c>
       <c r="C4" t="n">
-        <v>24.99999999999897</v>
+        <v>3430.824475167385</v>
       </c>
       <c r="D4" t="n">
-        <v>2499.895609982504</v>
+        <v>0.4363467172722436</v>
       </c>
       <c r="E4" t="n">
-        <v>249.9895609982523</v>
+        <v>4.850581212699952</v>
       </c>
       <c r="F4" t="n">
-        <v>24.99973902359305</v>
+        <v>3199.091310661691</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3316368823319442</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.472793151515725</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1239.504483838773</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2835761554704687</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.386420798982787</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2500.000000000005</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>249.9999999999995</v>
+        <v>0.2913533186509135</v>
       </c>
       <c r="C5" t="n">
-        <v>25.0000000000005</v>
+        <v>3425.908172342116</v>
       </c>
       <c r="D5" t="n">
-        <v>2499.895609982505</v>
+        <v>1.392036925925662</v>
       </c>
       <c r="E5" t="n">
-        <v>249.9895609982495</v>
+        <v>9.12374588314079</v>
       </c>
       <c r="F5" t="n">
-        <v>24.99973902359459</v>
+        <v>3194.541310206576</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.31246774086261</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.870679721175332</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1237.639940654856</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4638914014460329</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.614665715608002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2500.000000000002</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>249.9999999999968</v>
+        <v>0.574651237387848</v>
       </c>
       <c r="C6" t="n">
-        <v>25.00000000000108</v>
+        <v>3435.039872053876</v>
       </c>
       <c r="D6" t="n">
-        <v>2499.895609982503</v>
+        <v>1.710733240673076</v>
       </c>
       <c r="E6" t="n">
-        <v>249.9895609982468</v>
+        <v>12.49854761023296</v>
       </c>
       <c r="F6" t="n">
-        <v>24.99973902359516</v>
+        <v>3201.896021173638</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.674892798452896</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.505235772505255</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1243.929576862104</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3483422662187777</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.115675281475136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2500.000000000001</v>
+        <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>249.9999999999991</v>
+        <v>0.8577660879089355</v>
       </c>
       <c r="C7" t="n">
-        <v>25.00000000000065</v>
+        <v>3442.982448975341</v>
       </c>
       <c r="D7" t="n">
-        <v>2499.895609982502</v>
+        <v>1.804607095022862</v>
       </c>
       <c r="E7" t="n">
-        <v>249.9895609982492</v>
+        <v>14.3105200992885</v>
       </c>
       <c r="F7" t="n">
-        <v>24.99973902359472</v>
+        <v>3206.319469897807</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.800235754494486</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.354310909050408</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1254.449521067502</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1255308553564436</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.61879833489941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2500</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>249.9999999999968</v>
+        <v>1.14096438493271</v>
       </c>
       <c r="C8" t="n">
-        <v>25.00000000000095</v>
+        <v>3450.734017823841</v>
       </c>
       <c r="D8" t="n">
-        <v>2499.8956099825</v>
+        <v>0.4190011209124893</v>
       </c>
       <c r="E8" t="n">
-        <v>249.9895609982469</v>
+        <v>10.04534179158668</v>
       </c>
       <c r="F8" t="n">
-        <v>24.99973902359502</v>
+        <v>3215.711596412179</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3918032640277394</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.069716949841453</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1251.704514039519</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.1484996350942722</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.988222932885494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2500.000000000008</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>249.9999999999905</v>
+        <v>1.42406165208359</v>
       </c>
       <c r="C9" t="n">
-        <v>25.00000000000253</v>
+        <v>3454.545407051633</v>
       </c>
       <c r="D9" t="n">
-        <v>2499.895609982509</v>
+        <v>0.383040550839405</v>
       </c>
       <c r="E9" t="n">
-        <v>249.9895609982406</v>
+        <v>7.9721184450983</v>
       </c>
       <c r="F9" t="n">
-        <v>24.9997390235966</v>
+        <v>3224.790729748224</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.001297899864932282</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.966935677647149</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1238.793250995279</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3830383519222265</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.399457087339651</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2500.000000000007</v>
+        <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>249.9999999999967</v>
+        <v>1.7074803074791</v>
       </c>
       <c r="C10" t="n">
-        <v>25.00000000000081</v>
+        <v>3455.836142740482</v>
       </c>
       <c r="D10" t="n">
-        <v>2499.895609982507</v>
+        <v>1.200027655748264</v>
       </c>
       <c r="E10" t="n">
-        <v>249.9895609982468</v>
+        <v>13.27642068365213</v>
       </c>
       <c r="F10" t="n">
-        <v>24.99973902359488</v>
+        <v>3223.828152981893</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9929814199544357</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.267833768879845</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1244.883723691804</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.673835494899123</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.38779432504688</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2500.000000000007</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>249.9999999999809</v>
+        <v>1.99058901872177</v>
       </c>
       <c r="C11" t="n">
-        <v>25.00000000000927</v>
+        <v>3451.631199950931</v>
       </c>
       <c r="D11" t="n">
-        <v>2499.895609982509</v>
+        <v>2.907475988813726</v>
       </c>
       <c r="E11" t="n">
-        <v>249.9895609982309</v>
+        <v>20.3142873805875</v>
       </c>
       <c r="F11" t="n">
-        <v>24.99973902360336</v>
+        <v>3216.392193130705</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.84670022999019</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.36686046289046</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1252.429319539652</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5913665750633449</v>
+      </c>
+      <c r="K11" t="n">
+        <v>14.36187982894062</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.273708756823735</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3475.517517816417</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.451583770059394</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18.60054104390377</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3233.497730442951</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.353290089460011</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11.11844014070202</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1274.250542032091</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.687232665454666</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14.91175428859981</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2.57336932029266</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3463.952816131999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4424452271211182</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.070681790808676</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3227.240457865637</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05838093568822863</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.387762483558644</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1258.526177520356</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.438576612863049</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.206255420288948</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.85649400558014</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3464.560629532698</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.149542013566049</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.751696051841163</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3231.482993030003</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8426610734031014</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.299512430249051</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1249.279000650318</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7819009888244289</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.466273592118889</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.139614041705325</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3472.493462359128</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.031873748780088</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12.78419612789315</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3240.864640277449</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8597367206221189</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.479340365113284</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1246.999290106535</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5706279038352375</v>
+      </c>
+      <c r="K15" t="n">
+        <v>11.02060883388263</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.422835405726625</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3465.7734194785</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.400681390580019</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.97430851263675</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3232.357903472935</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.386498380624093</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.756215189538091</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1250.379054135086</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1988230329814534</v>
+      </c>
+      <c r="K16" t="n">
+        <v>14.47522327183777</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.70636564101715</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3462.807145537607</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7660399840607095</v>
+      </c>
+      <c r="E17" t="n">
+        <v>13.26998913897647</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3231.293955794662</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7524195595221693</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.749823604047075</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1244.898669945148</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.143812598989785</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12.9819521604102</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.989467557330325</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3462.101119039213</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5405696086617978</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.113189164371587</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3232.283432365367</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.06056583083890832</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.682316889231799</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1240.358001267753</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5371659724364175</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.229410815837953</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4.272607739825441</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3457.117051816937</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.613516159848951</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10.99454043184462</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3222.744613383474</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.153622897839484</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.809114181376755</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1251.229581999736</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.128090691245228</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.57871010509911</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4.55571239795227</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3453.592390587457</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.278735716371141</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13.8826607522154</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3218.183952188191</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.03692112289633</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11.52524910960091</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1253.232799683276</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.021561943380946</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.739308917645371</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>